--- a/Terminal_44_OCT_arrivals_26.xlsx
+++ b/Terminal_44_OCT_arrivals_26.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA01AT7635 (8:23 PM)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WV1416 (9:33 PM)</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WT3991 (10:20 PM)</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WX1949 (9:12 PM)</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA51AM9636 (8:38 PM)</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AR20E5777 (9:24 PM)</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA51AN3487 (10:55 PM)</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NL02B5557 (12:49 AM)</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WW2336 (10:05 PM)</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WX6161 (10:41 PM)</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WQ2286 (10:59 PM)</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA51AN1904 (9:28 PM)</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA51AM9757 (11:12 PM)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA51AN3486 (11:54 PM)</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WX6464 (11:18 PM)</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WQ3834 (11:20 PM)</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WW3738 (10:31 PM)</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA01AT6904 (10:45 PM)</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP39WU3744 (11:24 PM)</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KA51AM9901 (10:59 PM)</t>
         </is>
       </c>
     </row>
@@ -1780,9 +1780,162 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AP39WX3045</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total buses=0 </t>
+          <t>AP39WX3045 (9:01 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AP39WV8788</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>AP39WV8788 (9:47 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AP39WV3009</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>AP39WV3009 (11:18 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KA51AM9758</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>KA51AM9758 (11:36 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AP39WQ3855</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AP39WQ3855 (11:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AP39WR3322</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>AP39WR3322 (12:23 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>KA01AT9112</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>KA01AT9112 (12:57 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>KA51AM6457</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>KA51AM6457 (1:05 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>KA51AM9755</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>KA51AM9755 (1:06 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total buses=29 </t>
         </is>
       </c>
     </row>
